--- a/OkostoltoRendszer/Documents/Ütemterv.xlsx
+++ b/OkostoltoRendszer/Documents/Ütemterv.xlsx
@@ -1,57 +1,134 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kovacs.mate.2022i_ba\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A68419-1822-40BA-B21B-79D637AB84F9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B730EF-56DB-4BD1-9478-1B5316F423AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{F69B6220-0BF3-4EB2-92FB-C1DCFD0C90E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{F69B6220-0BF3-4EB2-92FB-C1DCFD0C90E5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projekt ütemterv" sheetId="1" r:id="rId1"/>
+    <sheet name="Ütemterv" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Brainstorming</t>
   </si>
   <si>
-    <t>A projekt kezdete: 2025. október 17</t>
-  </si>
-  <si>
     <t>Specifikáció megírása</t>
   </si>
   <si>
     <t>Plusz két funkció kitalálása</t>
   </si>
   <si>
-    <t>A projekt megírása</t>
-  </si>
-  <si>
-    <t>Felhasználói dokumentáció</t>
-  </si>
-  <si>
-    <t>Fejlesztői dokumentáció</t>
-  </si>
-  <si>
     <t>Tesztelés</t>
   </si>
   <si>
-    <t>Tesztelési kézikönyv</t>
+    <t>Fejlesztés kezdete</t>
+  </si>
+  <si>
+    <t>Osztályok létrehozása</t>
+  </si>
+  <si>
+    <t>Projket kezdete:2025.10.17</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>Program elkészítése</t>
+  </si>
+  <si>
+    <t>Plusz két funkció beépítése</t>
+  </si>
+  <si>
+    <t>Osztályok módosítása</t>
+  </si>
+  <si>
+    <t>Hiba keresés a programban</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>T6</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>Felhasználói útmutató megírása</t>
+  </si>
+  <si>
+    <t>T8</t>
+  </si>
+  <si>
+    <t>T9</t>
+  </si>
+  <si>
+    <t>Fejlesztői dokumentáció megírása</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>PPt elkészítése</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>T11</t>
+  </si>
+  <si>
+    <t>Tesztelési jegyzőkönyv</t>
+  </si>
+  <si>
+    <t>Hibák javítása</t>
+  </si>
+  <si>
+    <t>Projekt leadása</t>
+  </si>
+  <si>
+    <t>T12</t>
   </si>
 </sst>
 </file>
@@ -85,19 +162,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -109,21 +174,71 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.499984740745262"/>
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="-0.499984740745262"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -132,38 +247,78 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -171,6 +326,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF66FF99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -186,32 +346,32 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>9527</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>9528</xdr:colOff>
+      <xdr:colOff>47625</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="Összekötő: szögletes 5">
+        <xdr:cNvPr id="3" name="Összekötő: szögletes 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB39BF66-36D7-4B05-AF3E-4749EC0D0CFE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{814C3FC6-980C-FF41-8112-EE32A0D518FD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm rot="16200000" flipH="1">
-          <a:off x="2986090" y="280986"/>
-          <a:ext cx="752475" cy="609601"/>
+        <a:xfrm>
+          <a:off x="3038475" y="400050"/>
+          <a:ext cx="666750" cy="638175"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -239,23 +399,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="Összekötő: szögletes 8">
+        <xdr:cNvPr id="6" name="Összekötő: szögletes 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9306844E-08C4-4115-A4AA-B68128C9E9C0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2D29210-CDA1-3680-789A-B35946E02DD0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -263,8 +423,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4267200" y="1333500"/>
-          <a:ext cx="1200150" cy="381000"/>
+          <a:off x="4895850" y="1143000"/>
+          <a:ext cx="590550" cy="476250"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -292,36 +452,39 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="Egyenes összekötő 11">
+        <xdr:cNvPr id="12" name="Egyenes összekötő nyíllal 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B0D0CFD-E941-4C9E-9F6F-183975F7B262}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41415597-7E9E-1191-19C4-B8F80176099F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="6705600" y="1905000"/>
-          <a:ext cx="1" cy="180975"/>
+        <a:xfrm>
+          <a:off x="6391275" y="1704975"/>
+          <a:ext cx="0" cy="428625"/>
         </a:xfrm>
-        <a:prstGeom prst="line">
+        <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="1">
@@ -342,23 +505,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="Összekötő: szögletes 20">
+        <xdr:cNvPr id="15" name="Összekötő: szögletes 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5340BEF7-334F-4CF9-A03E-87A9D504FF19}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D0AA251-5242-7E4A-8FA8-8C83FDA652CA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -366,8 +529,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7934325" y="1714500"/>
-          <a:ext cx="1228725" cy="200025"/>
+          <a:off x="7324725" y="1609725"/>
+          <a:ext cx="590550" cy="419100"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -395,23 +558,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>66678</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="24" name="Összekötő: szögletes 23">
+        <xdr:cNvPr id="20" name="Összekötő: szögletes 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17B7219D-3F66-405C-B163-D22C85914999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EC66059-D7DA-8015-E0C3-46D1C597C05B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -419,8 +582,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9820278" y="2085976"/>
-          <a:ext cx="1085847" cy="581024"/>
+          <a:off x="8553450" y="2114550"/>
+          <a:ext cx="590550" cy="476250"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -450,21 +613,21 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="30" name="Egyenes összekötő 29">
+        <xdr:cNvPr id="24" name="Összekötő: szögletes 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15A339AB-F1E6-4F75-AB0E-775504F0F6B5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3C25D7A-187E-1F5D-B73E-A6E7A33686F2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -472,12 +635,15 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10363200" y="2657475"/>
-          <a:ext cx="0" cy="600075"/>
+          <a:off x="10363200" y="2676525"/>
+          <a:ext cx="600075" cy="266700"/>
         </a:xfrm>
-        <a:prstGeom prst="line">
+        <a:prstGeom prst="bentConnector3">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="1">
@@ -498,137 +664,34 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="35" name="Egyenes összekötő nyíllal 34">
+        <xdr:cNvPr id="26" name="Összekötő: szögletes 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F878180-76E8-42AD-A169-7E62B7464FB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09CF5C01-1F85-82E8-1721-23D25A61E1D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="10363200" y="3238500"/>
-          <a:ext cx="609600" cy="9525"/>
+        <a:xfrm>
+          <a:off x="12192000" y="2933700"/>
+          <a:ext cx="590550" cy="228600"/>
         </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>171451</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="42" name="Egyenes összekötő 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22C95E13-FC0E-4652-81F9-56EEA5442187}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="10363200" y="3219451"/>
-          <a:ext cx="1" cy="990599"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="47" name="Egyenes összekötő nyíllal 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{196576F6-AFAD-4045-88F6-1355353D5502}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="10363200" y="4181475"/>
-          <a:ext cx="1219200" cy="19050"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
+        <a:prstGeom prst="bentConnector3">
           <a:avLst/>
         </a:prstGeom>
         <a:ln>
@@ -655,31 +718,455 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="52" name="Egyenes összekötő nyíllal 51">
+        <xdr:cNvPr id="28" name="Összekötő: szögletes 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{426D7506-34A7-494F-A69A-DDE2BA9F4788}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33E4381D-4A9D-3A82-BCBC-7DD5277B84C3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="14030325" y="4181476"/>
-          <a:ext cx="1219200" cy="9524"/>
+        <a:xfrm>
+          <a:off x="14144625" y="3238500"/>
+          <a:ext cx="485775" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="Összekötő: szögletes 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5568D31D-36B9-56CA-76FA-AA24A5943B57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15459075" y="3619500"/>
+          <a:ext cx="400050" cy="323850"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>176753</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>9820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>598995</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>88376</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Összekötő: szögletes 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{207A3380-02F6-6A20-22A2-AAE7C7EABE77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17223557" y="3927835"/>
+          <a:ext cx="422242" cy="265129"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>579356</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>19639</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>530258</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>98196</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Összekötő: szögletes 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C71FC68E-2B39-F7B7-6857-ED73EB2D9457}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19452603" y="4310799"/>
+          <a:ext cx="559717" cy="265129"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>9819</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>108015</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>510618</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>108015</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Egyenes összekötő nyíllal 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60236BE9-05FB-8197-E57D-C270037A64CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19491881" y="4212603"/>
+          <a:ext cx="500799" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>108015</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>569536</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>108015</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Egyenes összekötő nyíllal 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58495C3E-7D33-1B71-8CBA-B6880C8C5EEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22526134" y="4585747"/>
+          <a:ext cx="569536" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>29459</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>117835</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>569536</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>108015</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="Összekötő: szögletes 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF5301EA-E388-998A-14E8-BE5D4DD8F21D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24382036" y="4222423"/>
+          <a:ext cx="540077" cy="176752"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>98196</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>49098</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>98196</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>176753</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="Egyenes összekötő nyíllal 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A2B275B-308B-A7A2-6633-2745EF137472}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25668402" y="4526830"/>
+          <a:ext cx="0" cy="127655"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>29459</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>98196</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>569536</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>98196</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="Egyenes összekötő nyíllal 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27B9CFC5-5E6C-3E18-AA07-5A74D4B87886}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="26817294" y="4762500"/>
+          <a:ext cx="540077" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -709,9 +1196,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-téma">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 téma">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -749,7 +1236,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -855,7 +1342,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -997,149 +1484,905 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F41CEEB8-F1D5-4D32-BF0C-142F05196786}">
-  <dimension ref="A1:AB23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C7E57D0-7460-498F-92A5-3F23399223C4}">
+  <dimension ref="B1:AV32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H1" s="5"/>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="3"/>
+      <c r="Q1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S1" s="3"/>
+      <c r="T1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="V1" s="5"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z1" s="3"/>
+      <c r="AA1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH1" s="5"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AM1" s="5"/>
+      <c r="AN1" s="3"/>
+      <c r="AO1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+      <c r="AR1" s="1"/>
+      <c r="AT1" s="5"/>
+      <c r="AU1" s="3"/>
+      <c r="AV1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="P2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="1"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="1"/>
+      <c r="Z2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="3"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="3"/>
+      <c r="AP2" s="5"/>
+      <c r="AQ2" s="5"/>
+      <c r="AR2" s="1"/>
+      <c r="AT2" s="5"/>
+      <c r="AU2" s="3"/>
+    </row>
+    <row r="3" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="P3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="1"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="1"/>
+      <c r="Z3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="3"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" s="3"/>
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="3"/>
+      <c r="AP3" s="5"/>
+      <c r="AQ3" s="5"/>
+      <c r="AR3" s="1"/>
+      <c r="AT3" s="5"/>
+      <c r="AU3" s="3"/>
+    </row>
+    <row r="4" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H4" s="5"/>
+      <c r="I4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="P4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="1"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="1"/>
+      <c r="Z4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="3"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="3"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="3"/>
+      <c r="AP4" s="5"/>
+      <c r="AQ4" s="5"/>
+      <c r="AR4" s="1"/>
+      <c r="AT4" s="5"/>
+      <c r="AU4" s="3"/>
+    </row>
+    <row r="5" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H5" s="5"/>
+      <c r="I5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="P5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="1"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="1"/>
+      <c r="Z5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="3"/>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="3"/>
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="3"/>
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="5"/>
+      <c r="AN5" s="3"/>
+      <c r="AP5" s="5"/>
+      <c r="AQ5" s="5"/>
+      <c r="AR5" s="1"/>
+      <c r="AT5" s="5"/>
+      <c r="AU5" s="3"/>
+    </row>
+    <row r="6" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="G6" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="P6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="1"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="1"/>
+      <c r="Z6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="2"/>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="3"/>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="2"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="5"/>
+      <c r="AM6" s="5"/>
+      <c r="AN6" s="3"/>
+      <c r="AP6" s="5"/>
+      <c r="AQ6" s="5"/>
+      <c r="AR6" s="1"/>
+      <c r="AT6" s="5"/>
+      <c r="AU6" s="3"/>
+    </row>
+    <row r="7" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H7" s="5"/>
+      <c r="I7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="P7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="1"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="1"/>
+      <c r="Z7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="2"/>
+      <c r="AE7" s="5"/>
+      <c r="AF7" s="3"/>
+      <c r="AH7" s="5"/>
+      <c r="AI7" s="3"/>
+      <c r="AJ7" s="2"/>
+      <c r="AK7" s="3"/>
+      <c r="AL7" s="5"/>
+      <c r="AM7" s="5"/>
+      <c r="AN7" s="3"/>
+      <c r="AP7" s="5"/>
+      <c r="AQ7" s="5"/>
+      <c r="AR7" s="1"/>
+      <c r="AT7" s="5"/>
+      <c r="AU7" s="3"/>
+    </row>
+    <row r="8" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H8" s="5"/>
+      <c r="I8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="P8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="1"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="1"/>
+      <c r="Z8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="2"/>
+      <c r="AE8" s="5"/>
+      <c r="AF8" s="3"/>
+      <c r="AH8" s="5"/>
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="2"/>
+      <c r="AK8" s="3"/>
+      <c r="AL8" s="5"/>
+      <c r="AM8" s="5"/>
+      <c r="AN8" s="3"/>
+      <c r="AP8" s="5"/>
+      <c r="AQ8" s="5"/>
+      <c r="AR8" s="1"/>
+      <c r="AT8" s="5"/>
+      <c r="AU8" s="3"/>
+    </row>
+    <row r="9" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H9" s="5"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="G6" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="J9" s="9" t="s">
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="2"/>
+      <c r="P9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="1"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="1"/>
+      <c r="Z9" s="3"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="2"/>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="3"/>
+      <c r="AH9" s="5"/>
+      <c r="AI9" s="3"/>
+      <c r="AJ9" s="2"/>
+      <c r="AK9" s="3"/>
+      <c r="AL9" s="5"/>
+      <c r="AM9" s="5"/>
+      <c r="AN9" s="3"/>
+      <c r="AP9" s="5"/>
+      <c r="AQ9" s="5"/>
+      <c r="AR9" s="1"/>
+      <c r="AT9" s="5"/>
+      <c r="AU9" s="3"/>
+    </row>
+    <row r="10" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H10" s="5"/>
+      <c r="I10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="P10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="1"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="1"/>
+      <c r="Z10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="3"/>
+      <c r="AH10" s="5"/>
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="2"/>
+      <c r="AK10" s="3"/>
+      <c r="AL10" s="5"/>
+      <c r="AM10" s="5"/>
+      <c r="AN10" s="3"/>
+      <c r="AP10" s="5"/>
+      <c r="AQ10" s="5"/>
+      <c r="AR10" s="1"/>
+      <c r="AT10" s="5"/>
+      <c r="AU10" s="3"/>
+    </row>
+    <row r="11" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H11" s="5"/>
+      <c r="I11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="9"/>
+      <c r="P11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="1"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="1"/>
+      <c r="Z11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="2"/>
+      <c r="AE11" s="5"/>
+      <c r="AF11" s="3"/>
+      <c r="AH11" s="5"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="2"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="5"/>
+      <c r="AM11" s="5"/>
+      <c r="AN11" s="3"/>
+      <c r="AP11" s="5"/>
+      <c r="AQ11" s="5"/>
+      <c r="AR11" s="1"/>
+      <c r="AT11" s="5"/>
+      <c r="AU11" s="3"/>
+    </row>
+    <row r="12" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H12" s="5"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="8" t="s">
         <v>2</v>
-      </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="J12" s="9" t="s">
-        <v>3</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S14" s="4" t="s">
+      <c r="M12" s="2"/>
+      <c r="P12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="1"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="1"/>
+      <c r="Z12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="2"/>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="3"/>
+      <c r="AH12" s="5"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="2"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="5"/>
+      <c r="AM12" s="5"/>
+      <c r="AN12" s="3"/>
+      <c r="AP12" s="5"/>
+      <c r="AQ12" s="5"/>
+      <c r="AR12" s="1"/>
+      <c r="AT12" s="5"/>
+      <c r="AU12" s="3"/>
+    </row>
+    <row r="13" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H13" s="5"/>
+      <c r="I13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="P13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="1"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="1"/>
+      <c r="Z13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="2"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="3"/>
+      <c r="AH13" s="5"/>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="5"/>
+      <c r="AM13" s="5"/>
+      <c r="AN13" s="3"/>
+      <c r="AP13" s="5"/>
+      <c r="AQ13" s="5"/>
+      <c r="AR13" s="1"/>
+      <c r="AT13" s="5"/>
+      <c r="AU13" s="3"/>
+    </row>
+    <row r="14" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H14" s="5"/>
+      <c r="I14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="P14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-    </row>
-    <row r="17" spans="19:28" x14ac:dyDescent="0.25">
-      <c r="S17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-    </row>
-    <row r="18" spans="19:28" x14ac:dyDescent="0.25">
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-    </row>
-    <row r="22" spans="19:28" x14ac:dyDescent="0.25">
-      <c r="T22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="U22" s="5"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="1"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="1"/>
+      <c r="Z14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="2"/>
+      <c r="AE14" s="5"/>
+      <c r="AF14" s="3"/>
+      <c r="AH14" s="5"/>
+      <c r="AI14" s="3"/>
+      <c r="AJ14" s="2"/>
+      <c r="AK14" s="3"/>
+      <c r="AL14" s="5"/>
+      <c r="AM14" s="5"/>
+      <c r="AN14" s="3"/>
+      <c r="AP14" s="5"/>
+      <c r="AQ14" s="5"/>
+      <c r="AR14" s="1"/>
+      <c r="AT14" s="5"/>
+      <c r="AU14" s="3"/>
+    </row>
+    <row r="15" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H15" s="5"/>
+      <c r="I15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="P15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="1"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="1"/>
+      <c r="Z15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="3"/>
+      <c r="AH15" s="5"/>
+      <c r="AI15" s="3"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="3"/>
+      <c r="AL15" s="5"/>
+      <c r="AM15" s="5"/>
+      <c r="AN15" s="3"/>
+      <c r="AP15" s="5"/>
+      <c r="AQ15" s="5"/>
+      <c r="AR15" s="1"/>
+      <c r="AT15" s="5"/>
+      <c r="AU15" s="3"/>
+    </row>
+    <row r="16" spans="2:48" x14ac:dyDescent="0.25">
+      <c r="H16" s="5"/>
+      <c r="I16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="P16" s="3"/>
+      <c r="S16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="T16" s="12"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="1"/>
+      <c r="Z16" s="3"/>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="5"/>
+      <c r="AF16" s="3"/>
+      <c r="AH16" s="5"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="5"/>
+      <c r="AM16" s="5"/>
+      <c r="AN16" s="3"/>
+      <c r="AP16" s="5"/>
+      <c r="AQ16" s="5"/>
+      <c r="AR16" s="1"/>
+      <c r="AT16" s="5"/>
+      <c r="AU16" s="3"/>
+    </row>
+    <row r="17" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="H17" s="5"/>
+      <c r="I17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="P17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="1"/>
+      <c r="V17" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="W17" s="13"/>
+      <c r="X17" s="14"/>
+      <c r="Z17" s="3"/>
+      <c r="AC17" s="3"/>
+      <c r="AD17" s="2"/>
+      <c r="AE17" s="5"/>
+      <c r="AF17" s="3"/>
+      <c r="AH17" s="5"/>
+      <c r="AI17" s="3"/>
+      <c r="AJ17" s="2"/>
+      <c r="AK17" s="3"/>
+      <c r="AL17" s="5"/>
+      <c r="AM17" s="5"/>
+      <c r="AN17" s="3"/>
+      <c r="AP17" s="5"/>
+      <c r="AQ17" s="5"/>
+      <c r="AR17" s="1"/>
+      <c r="AT17" s="5"/>
+      <c r="AU17" s="3"/>
+    </row>
+    <row r="18" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="H18" s="5"/>
+      <c r="I18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="P18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="1"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="1"/>
+      <c r="Z18" s="3"/>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="2"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="3"/>
+      <c r="AH18" s="5"/>
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="2"/>
+      <c r="AK18" s="3"/>
+      <c r="AL18" s="5"/>
+      <c r="AM18" s="5"/>
+      <c r="AN18" s="3"/>
+      <c r="AP18" s="5"/>
+      <c r="AQ18" s="5"/>
+      <c r="AR18" s="1"/>
+      <c r="AT18" s="5"/>
+      <c r="AU18" s="3"/>
+    </row>
+    <row r="19" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="H19" s="5"/>
+      <c r="I19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="P19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="1"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z19" s="9"/>
+      <c r="AA19" s="9"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="5"/>
+      <c r="AF19" s="3"/>
+      <c r="AH19" s="5"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="5"/>
+      <c r="AM19" s="5"/>
+      <c r="AN19" s="3"/>
+      <c r="AP19" s="5"/>
+      <c r="AQ19" s="5"/>
+      <c r="AR19" s="1"/>
+      <c r="AT19" s="5"/>
+      <c r="AU19" s="3"/>
+    </row>
+    <row r="20" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="H20" s="5"/>
+      <c r="I20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="P20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="1"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="1"/>
+      <c r="Z20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="2"/>
+      <c r="AE20" s="5"/>
+      <c r="AF20" s="3"/>
+      <c r="AH20" s="5"/>
+      <c r="AI20" s="3"/>
+      <c r="AJ20" s="2"/>
+      <c r="AK20" s="3"/>
+      <c r="AL20" s="5"/>
+      <c r="AM20" s="5"/>
+      <c r="AN20" s="3"/>
+      <c r="AP20" s="5"/>
+      <c r="AQ20" s="5"/>
+      <c r="AR20" s="1"/>
+      <c r="AT20" s="5"/>
+      <c r="AU20" s="3"/>
+    </row>
+    <row r="21" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="H21" s="5"/>
+      <c r="I21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="P21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="1"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="1"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB21" s="15"/>
+      <c r="AC21" s="16"/>
+      <c r="AD21" s="2"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="3"/>
+      <c r="AH21" s="5"/>
+      <c r="AI21" s="3"/>
+      <c r="AJ21" s="2"/>
+      <c r="AK21" s="3"/>
+      <c r="AL21" s="5"/>
+      <c r="AM21" s="5"/>
+      <c r="AN21" s="3"/>
+      <c r="AP21" s="5"/>
+      <c r="AQ21" s="5"/>
+      <c r="AR21" s="1"/>
+      <c r="AT21" s="5"/>
+      <c r="AU21" s="3"/>
+    </row>
+    <row r="22" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="I22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="T22" s="6"/>
       <c r="V22" s="5"/>
       <c r="W22" s="5"/>
-      <c r="Z22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA22" s="6"/>
-      <c r="AB22" s="6"/>
-    </row>
-    <row r="23" spans="19:28" x14ac:dyDescent="0.25">
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
+      <c r="X22" s="6"/>
+      <c r="AA22" s="2"/>
+      <c r="AD22" s="2"/>
+      <c r="AE22" s="5"/>
+      <c r="AF22" s="3"/>
+      <c r="AH22" s="5"/>
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="2"/>
+      <c r="AK22" s="3"/>
+      <c r="AL22" s="5"/>
+      <c r="AM22" s="5"/>
+      <c r="AN22" s="3"/>
+      <c r="AP22" s="5"/>
+      <c r="AQ22" s="5"/>
+      <c r="AR22" s="1"/>
+      <c r="AT22" s="5"/>
+      <c r="AU22" s="3"/>
+    </row>
+    <row r="23" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="I23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="T23" s="6"/>
       <c r="V23" s="5"/>
       <c r="W23" s="5"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="6"/>
-      <c r="AB23" s="6"/>
+      <c r="X23" s="6"/>
+      <c r="AA23" s="2"/>
+      <c r="AD23" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE23" s="18"/>
+      <c r="AF23" s="19"/>
+      <c r="AH23" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI23" s="20"/>
+      <c r="AJ23" s="20"/>
+      <c r="AK23" s="20"/>
+      <c r="AL23" s="20"/>
+      <c r="AM23" s="20"/>
+      <c r="AN23" s="21"/>
+      <c r="AP23" s="5"/>
+      <c r="AQ23" s="5"/>
+      <c r="AR23" s="1"/>
+      <c r="AT23" s="5"/>
+      <c r="AU23" s="3"/>
+    </row>
+    <row r="24" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="I24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="T24" s="6"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="6"/>
+      <c r="AA24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AE24" s="5"/>
+      <c r="AF24" s="3"/>
+      <c r="AH24" s="5"/>
+      <c r="AI24" s="3"/>
+      <c r="AJ24" s="5"/>
+      <c r="AK24" s="3"/>
+      <c r="AL24" s="5"/>
+      <c r="AM24" s="5"/>
+      <c r="AN24" s="3"/>
+      <c r="AP24" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ24" s="20"/>
+      <c r="AR24" s="22"/>
+      <c r="AT24" s="5"/>
+      <c r="AU24" s="3"/>
+    </row>
+    <row r="25" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="I25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="T25" s="6"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="6"/>
+      <c r="AA25" s="2"/>
+      <c r="AD25" s="2"/>
+      <c r="AE25" s="5"/>
+      <c r="AF25" s="3"/>
+      <c r="AH25" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI25" s="18"/>
+      <c r="AJ25" s="18"/>
+      <c r="AK25" s="19"/>
+      <c r="AL25" s="5"/>
+      <c r="AM25" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN25" s="19"/>
+      <c r="AP25" s="5"/>
+      <c r="AQ25" s="5"/>
+      <c r="AR25" s="1"/>
+      <c r="AT25" s="5"/>
+      <c r="AU25" s="3"/>
+    </row>
+    <row r="26" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="I26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="T26" s="6"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="6"/>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="5"/>
+      <c r="AC26" s="3"/>
+      <c r="AD26" s="5"/>
+      <c r="AE26" s="5"/>
+      <c r="AF26" s="3"/>
+      <c r="AH26" s="5"/>
+      <c r="AI26" s="3"/>
+      <c r="AJ26" s="5"/>
+      <c r="AK26" s="3"/>
+      <c r="AL26" s="5"/>
+      <c r="AM26" s="5"/>
+      <c r="AN26" s="3"/>
+      <c r="AP26" s="5"/>
+      <c r="AQ26" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="AR26" s="24"/>
+      <c r="AT26" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="AU26" s="27"/>
+    </row>
+    <row r="27" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="I27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="3"/>
+      <c r="T27" s="6"/>
+      <c r="X27" s="6"/>
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="5"/>
+      <c r="AC27" s="3"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="5"/>
+      <c r="AI27" s="3"/>
+      <c r="AL27" s="2"/>
+      <c r="AM27" s="5"/>
+      <c r="AN27" s="3"/>
+      <c r="AQ27" s="5"/>
+      <c r="AR27" s="1"/>
+      <c r="AT27" s="5"/>
+      <c r="AU27" s="3"/>
+    </row>
+    <row r="28" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="I28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="3"/>
+      <c r="T28" s="6"/>
+      <c r="U28" t="s">
+        <v>24</v>
+      </c>
+      <c r="X28" s="6"/>
+      <c r="Y28" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="5"/>
+      <c r="AC28" s="3"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="5"/>
+      <c r="AI28" s="3"/>
+      <c r="AL28" s="2"/>
+      <c r="AM28" s="5"/>
+      <c r="AN28" s="3"/>
+      <c r="AQ28" s="5"/>
+      <c r="AR28" s="1"/>
+      <c r="AS28" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT28" s="5"/>
+      <c r="AU28" s="3"/>
+    </row>
+    <row r="29" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="AL29" s="5"/>
+      <c r="AM29" s="5"/>
+      <c r="AN29" s="5"/>
+      <c r="AO29" s="5"/>
+    </row>
+    <row r="30" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="AN30" s="5"/>
+      <c r="AO30" s="5"/>
+    </row>
+    <row r="32" spans="8:47" x14ac:dyDescent="0.25">
+      <c r="AD32" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="Z22:AB23"/>
-    <mergeCell ref="G6:I7"/>
-    <mergeCell ref="J12:M13"/>
-    <mergeCell ref="J9:M10"/>
-    <mergeCell ref="P10:S11"/>
-    <mergeCell ref="S14:U15"/>
-    <mergeCell ref="S17:U18"/>
-    <mergeCell ref="T22:W23"/>
-    <mergeCell ref="A1:E2"/>
+  <mergeCells count="17">
+    <mergeCell ref="AP24:AR24"/>
+    <mergeCell ref="AQ26:AR26"/>
+    <mergeCell ref="AT26:AU26"/>
+    <mergeCell ref="AH25:AK25"/>
+    <mergeCell ref="AH23:AN23"/>
+    <mergeCell ref="AM25:AN25"/>
+    <mergeCell ref="B2:E3"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="AA21:AC21"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="V17:X17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>